--- a/tables/Table S3.xlsx
+++ b/tables/Table S3.xlsx
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="12.6640625" customWidth="1" style="17" min="1" max="1"/>
@@ -660,25 +660,29 @@
         <v>3</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>10</v>
+        <v>6.763</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>0.02</v>
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>0.080*</t>
+        </is>
       </c>
       <c r="G3" s="16" t="n">
         <v>3</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>10.7</v>
+        <v>6.804</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>0.614</v>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>0.01</v>
+        <v>0.617</v>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>0.078*</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="23" customHeight="1" s="17">
@@ -691,10 +695,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>1.3</v>
+        <v>2.475</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>0.497</v>
+        <v>0.514</v>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
@@ -705,10 +709,10 @@
         <v>1</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.03</v>
+        <v>0.544</v>
       </c>
       <c r="I4" s="16" t="n">
-        <v>0.499</v>
+        <v>0.505</v>
       </c>
       <c r="J4" s="16" t="inlineStr">
         <is>
@@ -728,24 +732,28 @@
         </is>
       </c>
       <c r="C5" s="16" t="n">
-        <v>4.35</v>
+        <v>4.2077</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>4.8758</v>
+        <v>8.1243</v>
       </c>
       <c r="E5" s="16" t="n"/>
-      <c r="F5" s="23" t="n">
-        <v>0.01272</v>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
       </c>
       <c r="G5" s="24" t="n">
-        <v>4.404</v>
+        <v>4.7202</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>3.2015</v>
+        <v>31.0422</v>
       </c>
       <c r="I5" s="16" t="n"/>
-      <c r="J5" s="8" t="n">
-        <v>0.032756</v>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -758,22 +766,24 @@
         <v>3</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>2.861</v>
+        <v>11.214</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0.02906</v>
-      </c>
-      <c r="F6" s="23" t="n">
-        <v>0.03718</v>
+        <v>0.1611</v>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
       </c>
       <c r="G6" s="16" t="n">
         <v>3</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>21.446</v>
+        <v>30.036</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.17837</v>
+        <v>0.2336</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -791,10 +801,10 @@
         <v>3</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>41.653</v>
+        <v>37.297</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0.30357</v>
+        <v>0.3897</v>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
@@ -805,10 +815,10 @@
         <v>3</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>1.52</v>
+        <v>1.517</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.01515</v>
+        <v>0.0152</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -828,22 +838,22 @@
         </is>
       </c>
       <c r="C8" s="24" t="n">
-        <v>2.879</v>
+        <v>4.2161</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0.2922</v>
+        <v>13.6589</v>
       </c>
       <c r="E8" s="16" t="n"/>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="G8" s="24" t="n">
-        <v>8.633599999999999</v>
+        <v>9.5312</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>3.1059</v>
+        <v>7.6718</v>
       </c>
       <c r="I8" s="8" t="n"/>
       <c r="J8" s="10" t="inlineStr">
@@ -862,10 +872,10 @@
         <v>1</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.295</v>
+        <v>0.867</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>0.0006569</v>
+        <v>0.0021</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -876,10 +886,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>2.13</v>
+        <v>1.298</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.00439</v>
+        <v>0.0029</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -897,10 +907,10 @@
         <v>3</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>10.652</v>
+        <v>7.254</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0.06647</v>
+        <v>0.0501</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
@@ -911,10 +921,10 @@
         <v>3</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>0.492</v>
+        <v>0.428</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.003046</v>
+        <v>0.0029</v>
       </c>
       <c r="J10" s="10" t="inlineStr">
         <is>
@@ -937,10 +947,10 @@
         <v>1</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>0.02</v>
+        <v>0.0025</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0001</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -951,10 +961,10 @@
         <v>1</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.7235</v>
+        <v>0.9956</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>0.0786</v>
+        <v>0.0895</v>
       </c>
       <c r="J11" s="13" t="inlineStr">
         <is>
@@ -972,487 +982,473 @@
         <v>3</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>4.3</v>
+        <v>5.3111</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>0.2848</v>
+        <v>0.4027</v>
       </c>
       <c r="F12" s="23" t="n">
-        <v>0.02</v>
+        <v>0.012</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>2.798</v>
+        <v>3.5537</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>0.1227</v>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
-        <is>
-          <t>0.074*</t>
-        </is>
+        <v>0.1475</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>0.038</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Site/Genotype</t>
+          <t>pH × Site</t>
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>23.284</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
+        <v>4.7541</v>
+      </c>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>3.6736</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>0.1575</v>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>0.055*</t>
-        </is>
+        <v>4.4969</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>0.06660000000000001</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>0.0069</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="11" t="inlineStr">
         <is>
+          <t>Site/Genotype</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>4.8934</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0.4558</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>8.689299999999999</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>0.2162</v>
+      </c>
+      <c r="J14" s="16" t="n">
+        <v>0.0032</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="11" t="inlineStr">
+        <is>
           <t>pH/Tank</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>13.987</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>0.2278</v>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="C15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.7074</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0.0861</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>21.328</v>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>0.3896</v>
+      </c>
+      <c r="J15" s="16" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
       </c>
-      <c r="G14" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="9" t="n">
-        <v>16.773</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>0.3837</v>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Linear Mixed-Effects (Daytime Calcification)</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>pH</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>2.8181</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="9" t="n">
+      <c r="C16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>11.884</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="9" t="n">
         <v>1.9506</v>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I16" s="8" t="n">
         <v>0.0335</v>
       </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>0.5228</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>0.0492</v>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H16" s="9" t="n">
-        <v>5.8068</v>
-      </c>
-      <c r="I16" s="8" t="n">
-        <v>0.3401</v>
-      </c>
-      <c r="J16" s="8" t="n">
-        <v>0.007</v>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="11" t="inlineStr">
         <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>5.8068</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>0.007</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="11" t="inlineStr">
+        <is>
           <t>Site/Genotype</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>0.5719</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>0.2418</v>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="9" t="n">
+      <c r="C18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="8" t="n">
+      <c r="E18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="8" t="n">
         <v>0.0598</v>
       </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Linear Mixed-Effects (Nighttime Calcification)</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>pH</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>0.1522</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="9" t="n">
+      <c r="C19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>0.1423</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="9" t="n">
         <v>5.6812</v>
       </c>
-      <c r="I18" s="8" t="n">
+      <c r="I19" s="8" t="n">
         <v>0.0779</v>
       </c>
-      <c r="J18" s="16" t="n">
-        <v>0.0277</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>0.5756</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>0.0548</v>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H19" s="9" t="n">
-        <v>3.356</v>
-      </c>
-      <c r="I19" s="8" t="n">
-        <v>0.2607</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>0.0452</v>
+      <c r="J19" s="16" t="n">
+        <v>0.028</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="11" t="inlineStr">
         <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>0.5799</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>0.0694</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>3.356</v>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>0.2607</v>
+      </c>
+      <c r="J20" s="8" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="11" t="inlineStr">
+        <is>
           <t>Site/Genotype</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>0.2971</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>0.1977</v>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="9" t="n">
+      <c r="C21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="9" t="n">
         <v>1.0466</v>
       </c>
-      <c r="I20" s="8" t="n">
+      <c r="I21" s="8" t="n">
         <v>0.3056</v>
       </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>Linear Mixed-Effects (Day-Averaged Calcification)</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>pH</t>
         </is>
       </c>
-      <c r="C21" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>2.5452</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>0.0453</v>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="9" t="n">
+      <c r="C22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>8.717499999999999</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="9" t="n">
         <v>4.5799</v>
       </c>
-      <c r="I21" s="8" t="n">
+      <c r="I22" s="8" t="n">
         <v>0.0579</v>
       </c>
-      <c r="J21" s="16" t="n">
-        <v>0.0455</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>0.6853</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>0.0668</v>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>5.8999</v>
-      </c>
-      <c r="I22" s="8" t="n">
-        <v>0.3741</v>
-      </c>
-      <c r="J22" s="8" t="n">
-        <v>0.0065</v>
+      <c r="J22" s="16" t="n">
+        <v>0.046</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="11" t="inlineStr">
         <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0.4236</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>5.8999</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>0.0065</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="11" t="inlineStr">
+        <is>
           <t>Site/Genotype</t>
         </is>
       </c>
-      <c r="C23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>1.0077</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>0.2924</v>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="G23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="9" t="n">
+      <c r="C24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="9" t="n">
         <v>0.5532</v>
       </c>
-      <c r="I23" s="8" t="n">
+      <c r="I24" s="8" t="n">
         <v>0.2474</v>
       </c>
-      <c r="J23" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>PERMANOVA (Transcriptomics)</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Site</t>
         </is>
       </c>
-      <c r="C24" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" s="15" t="n">
+      <c r="C25" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="15" t="n">
         <v>3.2174</v>
       </c>
-      <c r="E24" s="14" t="n">
+      <c r="E25" s="14" t="n">
         <v>0.132</v>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
       </c>
-      <c r="G24" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="H24" s="14" t="n">
+      <c r="G25" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" s="14" t="n">
         <v>2.0138</v>
       </c>
-      <c r="I24" s="14" t="n">
+      <c r="I25" s="14" t="n">
         <v>0.075</v>
-      </c>
-      <c r="J24" s="14" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Treatment</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D25" s="15" t="n">
-        <v>2.0445</v>
-      </c>
-      <c r="E25" s="14" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-      <c r="G25" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="14" t="n">
-        <v>1.8964</v>
-      </c>
-      <c r="I25" s="14" t="n">
-        <v>0.07000000000000001</v>
       </c>
       <c r="J25" s="14" t="inlineStr">
         <is>
@@ -1463,33 +1459,68 @@
     <row r="26">
       <c r="B26" s="11" t="inlineStr">
         <is>
+          <t>Treatment</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>2.0445</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>1.8964</v>
+      </c>
+      <c r="I26" s="14" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="11" t="inlineStr">
+        <is>
           <t>Site:Treatment</t>
         </is>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C27" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="D26" s="15" t="n">
+      <c r="D27" s="15" t="n">
         <v>0.7974</v>
       </c>
-      <c r="E26" s="14" t="n">
+      <c r="E27" s="14" t="n">
         <v>0.098</v>
       </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="G26" s="14" t="n">
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="H26" s="14" t="n">
+      <c r="H27" s="14" t="n">
         <v>0.902</v>
       </c>
-      <c r="I26" s="14" t="n">
+      <c r="I27" s="14" t="n">
         <v>0.1</v>
       </c>
-      <c r="J26" s="14" t="inlineStr">
+      <c r="J27" s="14" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
@@ -1497,17 +1528,17 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A21:A23"/>
     <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A16:A18"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="A11:A15"/>
+    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tables/Table S3.xlsx
+++ b/tables/Table S3.xlsx
@@ -1424,107 +1424,79 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Site</t>
+          <t>Colony (genotype)</t>
         </is>
       </c>
       <c r="C25" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D25" s="15" t="n">
-        <v>3.2174</v>
+        <v>20</v>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="E25" s="14" t="n">
-        <v>0.132</v>
+        <v>0.642</v>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-      <c r="G25" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="14" t="n">
-        <v>2.0138</v>
-      </c>
-      <c r="I25" s="14" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="J25" s="14" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="n"/>
+      <c r="H25" s="14" t="n"/>
+      <c r="I25" s="14" t="n"/>
+      <c r="J25" s="14" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Treatment</t>
+          <t>Treatment (within colony)</t>
         </is>
       </c>
       <c r="C26" s="14" t="n">
         <v>3</v>
       </c>
       <c r="D26" s="15" t="n">
-        <v>2.0445</v>
+        <v>2.3162</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
       </c>
-      <c r="G26" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" s="14" t="n">
-        <v>1.8964</v>
-      </c>
-      <c r="I26" s="14" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J26" s="14" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
+      <c r="G26" s="14" t="n"/>
+      <c r="H26" s="14" t="n"/>
+      <c r="I26" s="14" t="n"/>
+      <c r="J26" s="14" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Site:Treatment</t>
+          <t>Urban vs Reef (colony means)</t>
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D27" s="15" t="n">
-        <v>0.7974</v>
+        <v>1.4387</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>0.098</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="H27" s="14" t="n">
-        <v>0.902</v>
-      </c>
-      <c r="I27" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J27" s="14" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
+          <t>0.094*</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="n"/>
+      <c r="H27" s="14" t="n"/>
+      <c r="I27" s="14" t="n"/>
+      <c r="J27" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -1534,8 +1506,8 @@
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B1:B2"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="A11:A15"/>
     <mergeCell ref="A22:A24"/>

--- a/tables/Table S3.xlsx
+++ b/tables/Table S3.xlsx
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="12.6640625" customWidth="1" style="17" min="1" max="1"/>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" s="17">
       <c r="A22" s="18" t="inlineStr">
         <is>
           <t>Linear Mixed-Effects (Day-Averaged Calcification)</t>
@@ -1348,7 +1348,7 @@
         <v>0.046</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" s="17">
       <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Site</t>
@@ -1381,7 +1381,7 @@
         <v>0.0065</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" s="17">
       <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Site/Genotype</t>
@@ -1416,100 +1416,572 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" s="17">
       <c r="A25" s="18" t="inlineStr">
         <is>
+          <t>Linear Mixed-Effects (Net Photosynthesis)</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>3.6351</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0.1158</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>0.086*</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>3.2872</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>0.0606</v>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>0.086*</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" s="17">
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>0.0396</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>1.0588</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" s="17">
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Site/Genotype</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0.2577</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0.2832</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>0.6834</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>0.2648</v>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" s="17">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>Linear Mixed-Effects (Respiration)</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0.2244</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>1.0659</v>
+      </c>
+      <c r="I28" s="8" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" s="17">
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0.0672</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>1.4174</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" s="17">
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>Site/Genotype</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>1.0958</v>
+      </c>
+      <c r="I30" s="8" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" s="17">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>Linear Mixed-Effects (Gross Photosynthesis)</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>1.574</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>5.2864</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <v>0.08359999999999999</v>
+      </c>
+      <c r="J31" s="16" t="n">
+        <v>0.033</v>
+      </c>
+    </row>
+    <row r="32" s="17">
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>0.0682</v>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>0.7875</v>
+      </c>
+      <c r="I32" s="8" t="n">
+        <v>0.0868</v>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" s="17">
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Site/Genotype</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>2.4509</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>2.5534</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>0.4158</v>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" s="17">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>Linear Mixed-Effects (Photosynthesis:Respiration)</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>3.2377</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>0.1183</v>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>0.096*</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>6.5486</v>
+      </c>
+      <c r="I34" s="8" t="n">
+        <v>0.1469</v>
+      </c>
+      <c r="J34" s="16" t="n">
+        <v>0.019</v>
+      </c>
+    </row>
+    <row r="35" s="17">
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>1.749</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" s="17">
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>Site/Genotype</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>0.1303</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="8" t="n">
+        <v>0.06279999999999999</v>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
           <t>PERMANOVA (Transcriptomics)</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>Colony (genotype)</t>
         </is>
       </c>
-      <c r="C25" s="14" t="n">
+      <c r="C37" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D37" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="E25" s="14" t="n">
-        <v>0.642</v>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="E37" s="14" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G25" s="14" t="n"/>
-      <c r="H25" s="14" t="n"/>
-      <c r="I25" s="14" t="n"/>
-      <c r="J25" s="14" t="n"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="11" t="inlineStr">
+      <c r="G37" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="H37" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>Treatment (within colony)</t>
         </is>
       </c>
-      <c r="C26" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D26" s="15" t="n">
+      <c r="C38" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" s="15" t="n">
         <v>2.3162</v>
       </c>
-      <c r="E26" s="14" t="n">
+      <c r="E38" s="14" t="n">
         <v>0.076</v>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
       </c>
-      <c r="G26" s="14" t="n"/>
-      <c r="H26" s="14" t="n"/>
-      <c r="I26" s="14" t="n"/>
-      <c r="J26" s="14" t="n"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="11" t="inlineStr">
+      <c r="G38" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>2.7452</v>
+      </c>
+      <c r="I38" s="14" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>Urban vs Reef (colony means)</t>
         </is>
       </c>
-      <c r="C27" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="15" t="n">
+      <c r="C39" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="15" t="n">
         <v>1.4387</v>
       </c>
-      <c r="E27" s="14" t="n">
+      <c r="E39" s="14" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>0.094*</t>
         </is>
       </c>
-      <c r="G27" s="14" t="n"/>
-      <c r="H27" s="14" t="n"/>
-      <c r="I27" s="14" t="n"/>
-      <c r="J27" s="14" t="n"/>
+      <c r="G39" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>1.1302</v>
+      </c>
+      <c r="I39" s="14" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="16">
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A34:A36"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A31:A33"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="A11:A15"/>
+    <mergeCell ref="A37:A39"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>

--- a/tables/Table S3.xlsx
+++ b/tables/Table S3.xlsx
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="12.6640625" customWidth="1" style="17" min="1" max="1"/>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" s="17">
       <c r="B38" s="11" t="inlineStr">
         <is>
           <t>Treatment (within colony)</t>
@@ -1931,36 +1931,71 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" s="17">
       <c r="B39" s="11" t="inlineStr">
         <is>
+          <t>Site (colony means)</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" s="15" t="n">
+        <v>1.1536</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>0.9865</v>
+      </c>
+      <c r="I39" s="14" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="11" t="inlineStr">
+        <is>
           <t>Urban vs Reef (colony means)</t>
         </is>
       </c>
-      <c r="C39" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="15" t="n">
+      <c r="C40" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="15" t="n">
         <v>1.4387</v>
       </c>
-      <c r="E39" s="14" t="n">
+      <c r="E40" s="14" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F39" s="11" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>0.094*</t>
         </is>
       </c>
-      <c r="G39" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="15" t="n">
+      <c r="G40" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="15" t="n">
         <v>1.1302</v>
       </c>
-      <c r="I39" s="14" t="n">
+      <c r="I40" s="14" t="n">
         <v>0.059</v>
       </c>
-      <c r="J39" s="11" t="inlineStr">
+      <c r="J40" s="11" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
@@ -1974,14 +2009,14 @@
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A31:A33"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="C1:F1"/>
+    <mergeCell ref="A31:A33"/>
     <mergeCell ref="A11:A15"/>
-    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="A37:A40"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>

--- a/tables/Table S3.xlsx
+++ b/tables/Table S3.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="6380" yWindow="3380" windowWidth="26840" windowHeight="15680" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3400" yWindow="2880" windowWidth="26840" windowHeight="15680" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -20,7 +20,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -44,11 +44,6 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="12"/>
-    </font>
-    <font>
       <name val="Times New Roman"/>
       <family val="1"/>
       <color rgb="FF000000"/>
@@ -58,6 +53,20 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <color theme="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <vertAlign val="subscript"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <i val="1"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -104,69 +113,71 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -567,44 +578,44 @@
   <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col width="12.6640625" customWidth="1" style="17" min="1" max="1"/>
-    <col width="11" bestFit="1" customWidth="1" style="17" min="2" max="2"/>
-    <col width="4.1640625" bestFit="1" customWidth="1" style="17" min="3" max="3"/>
-    <col width="6.83203125" bestFit="1" customWidth="1" style="17" min="4" max="4"/>
-    <col width="8.6640625" bestFit="1" customWidth="1" style="17" min="5" max="5"/>
-    <col width="6" bestFit="1" customWidth="1" style="17" min="6" max="6"/>
-    <col width="4.1640625" bestFit="1" customWidth="1" style="17" min="7" max="7"/>
-    <col width="6.83203125" bestFit="1" customWidth="1" style="17" min="8" max="8"/>
-    <col width="8.6640625" bestFit="1" customWidth="1" style="17" min="9" max="9"/>
-    <col width="6" bestFit="1" customWidth="1" style="17" min="10" max="10"/>
+    <col width="16.33203125" customWidth="1" style="22" min="1" max="1"/>
+    <col width="10.83203125" bestFit="1" customWidth="1" style="22" min="2" max="2"/>
+    <col width="5.83203125" bestFit="1" customWidth="1" style="22" min="3" max="3"/>
+    <col width="7" bestFit="1" customWidth="1" style="22" min="4" max="4"/>
+    <col width="8.6640625" bestFit="1" customWidth="1" style="22" min="5" max="5"/>
+    <col width="6" bestFit="1" customWidth="1" style="22" min="6" max="6"/>
+    <col width="4.1640625" bestFit="1" customWidth="1" style="22" min="7" max="7"/>
+    <col width="7" bestFit="1" customWidth="1" style="22" min="8" max="8"/>
+    <col width="8.6640625" bestFit="1" customWidth="1" style="22" min="9" max="9"/>
+    <col width="6" bestFit="1" customWidth="1" style="22" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="B1" s="20" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>Response (Test)</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="C1" s="26" t="inlineStr">
+      <c r="C1" s="21" t="inlineStr">
         <is>
           <t>Orbicella faveolata</t>
         </is>
       </c>
-      <c r="F1" s="27" t="n"/>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="F1" s="20" t="n"/>
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>Siderastrea siderea</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1" s="17">
-      <c r="B2" s="27" t="n"/>
-      <c r="C2" s="19" t="inlineStr">
+    <row r="2" ht="28" customHeight="1" s="22">
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="26" t="inlineStr">
         <is>
           <t>df</t>
         </is>
@@ -614,7 +625,7 @@
           <t>Test Statistic</t>
         </is>
       </c>
-      <c r="E2" s="19" t="inlineStr">
+      <c r="E2" s="26" t="inlineStr">
         <is>
           <t>Variance Explained</t>
         </is>
@@ -624,7 +635,7 @@
           <t>p</t>
         </is>
       </c>
-      <c r="G2" s="19" t="inlineStr">
+      <c r="G2" s="26" t="inlineStr">
         <is>
           <t>df</t>
         </is>
@@ -634,7 +645,7 @@
           <t>Test Statistic</t>
         </is>
       </c>
-      <c r="I2" s="19" t="inlineStr">
+      <c r="I2" s="26" t="inlineStr">
         <is>
           <t>Variance Explained</t>
         </is>
@@ -645,10 +656,10 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="23" customHeight="1" s="17">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>Cox Proportional Hazards (Survivorship)</t>
+    <row r="3" ht="23" customHeight="1" s="22">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>Survivorship (Cox Proportional Hazards)</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -656,13 +667,13 @@
           <t>Site</t>
         </is>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="25" t="n">
         <v>3</v>
       </c>
       <c r="D3" s="7" t="n">
         <v>6.763</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="25" t="n">
         <v>0.6830000000000001</v>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -670,7 +681,7 @@
           <t>0.080*</t>
         </is>
       </c>
-      <c r="G3" s="16" t="n">
+      <c r="G3" s="25" t="n">
         <v>3</v>
       </c>
       <c r="H3" s="7" t="n">
@@ -685,19 +696,19 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="23" customHeight="1" s="17">
+    <row r="4" ht="23" customHeight="1" s="22">
       <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Treatment</t>
         </is>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>2.475</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="25" t="n">
         <v>0.514</v>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -705,25 +716,82 @@
           <t>ns</t>
         </is>
       </c>
-      <c r="G4" s="16" t="n">
+      <c r="G4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>0.544</v>
       </c>
-      <c r="I4" s="16" t="n">
+      <c r="I4" s="25" t="n">
         <v>0.505</v>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="25" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>GAMM (Photosynthesis All Treatments)</t>
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <i val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>F</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>V</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>/</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <i val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>F</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>M</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>, Pre-Heat (GAMM)</t>
+          </r>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -731,25 +799,33 @@
           <t>Time</t>
         </is>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>4.2077</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>8.1243</v>
       </c>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
       </c>
-      <c r="G5" s="24" t="n">
+      <c r="G5" s="17" t="n">
         <v>4.7202</v>
       </c>
       <c r="H5" s="9" t="n">
         <v>31.0422</v>
       </c>
-      <c r="I5" s="16" t="n"/>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
@@ -762,7 +838,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="25" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="7" t="n">
@@ -771,12 +847,12 @@
       <c r="E6" s="8" t="n">
         <v>0.1611</v>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
       </c>
-      <c r="G6" s="16" t="n">
+      <c r="G6" s="25" t="n">
         <v>3</v>
       </c>
       <c r="H6" s="9" t="n">
@@ -785,7 +861,7 @@
       <c r="I6" s="8" t="n">
         <v>0.2336</v>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J6" s="25" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -797,7 +873,7 @@
           <t>Site</t>
         </is>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="25" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="7" t="n">
@@ -811,7 +887,7 @@
           <t>&lt;0.001</t>
         </is>
       </c>
-      <c r="G7" s="16" t="n">
+      <c r="G7" s="25" t="n">
         <v>3</v>
       </c>
       <c r="H7" s="9" t="n">
@@ -820,16 +896,73 @@
       <c r="I7" s="8" t="n">
         <v>0.0152</v>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="J7" s="25" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>GAMM (Photosynthesis Heat Treatments)</t>
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <i val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>F</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>V</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>/</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <i val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>F</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>M</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>, Heat Stress (GAMM)</t>
+          </r>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -837,25 +970,33 @@
           <t>Time</t>
         </is>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="17" t="n">
         <v>4.2161</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>13.6589</v>
       </c>
-      <c r="E8" s="16" t="n"/>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
       </c>
-      <c r="G8" s="24" t="n">
+      <c r="G8" s="17" t="n">
         <v>9.5312</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>7.6718</v>
       </c>
-      <c r="I8" s="8" t="n"/>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
       <c r="J8" s="10" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
@@ -868,7 +1009,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="7" t="n">
@@ -882,7 +1023,7 @@
           <t>ns</t>
         </is>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="7" t="n">
@@ -891,7 +1032,7 @@
       <c r="I9" s="8" t="n">
         <v>0.0029</v>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="J9" s="25" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
@@ -903,7 +1044,7 @@
           <t>Site</t>
         </is>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="25" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="7" t="n">
@@ -917,7 +1058,7 @@
           <t>&lt;0.001</t>
         </is>
       </c>
-      <c r="G10" s="16" t="n">
+      <c r="G10" s="25" t="n">
         <v>3</v>
       </c>
       <c r="H10" s="7" t="n">
@@ -933,9 +1074,9 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>Linear Mixed-Effects (Growth Rate)</t>
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>Growth Rate (Linear Mixed-Effects)</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
@@ -946,7 +1087,7 @@
       <c r="C11" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="9" t="n">
         <v>0.0025</v>
       </c>
       <c r="E11" s="8" t="n">
@@ -987,7 +1128,7 @@
       <c r="E12" s="8" t="n">
         <v>0.4027</v>
       </c>
-      <c r="F12" s="23" t="n">
+      <c r="F12" s="16" t="n">
         <v>0.012</v>
       </c>
       <c r="G12" s="12" t="n">
@@ -1016,7 +1157,7 @@
         <v>4.7541</v>
       </c>
       <c r="E13" s="8" t="n"/>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
@@ -1061,7 +1202,7 @@
       <c r="I14" s="8" t="n">
         <v>0.2162</v>
       </c>
-      <c r="J14" s="16" t="n">
+      <c r="J14" s="25" t="n">
         <v>0.0032</v>
       </c>
     </row>
@@ -1094,16 +1235,16 @@
       <c r="I15" s="8" t="n">
         <v>0.3896</v>
       </c>
-      <c r="J15" s="16" t="inlineStr">
+      <c r="J15" s="25" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>Linear Mixed-Effects (Daytime Calcification)</t>
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>Daytime Calcification (Linear Mixed-Effects)</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
@@ -1200,16 +1341,16 @@
       <c r="I18" s="8" t="n">
         <v>0.0598</v>
       </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="J18" s="25" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>Linear Mixed-Effects (Nighttime Calcification)</t>
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>Nighttime Calcification (Linear Mixed-Effects)</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
@@ -1226,7 +1367,7 @@
       <c r="E19" s="8" t="n">
         <v>0.0057</v>
       </c>
-      <c r="F19" s="23" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
@@ -1240,7 +1381,7 @@
       <c r="I19" s="8" t="n">
         <v>0.0779</v>
       </c>
-      <c r="J19" s="16" t="n">
+      <c r="J19" s="25" t="n">
         <v>0.028</v>
       </c>
     </row>
@@ -1306,16 +1447,16 @@
       <c r="I21" s="8" t="n">
         <v>0.3056</v>
       </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" s="17">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>Linear Mixed-Effects (Day-Averaged Calcification)</t>
+      <c r="J21" s="25" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1" s="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>Day-Averaged Calcification (Linear Mixed-Effects)</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
@@ -1344,11 +1485,11 @@
       <c r="I22" s="8" t="n">
         <v>0.0579</v>
       </c>
-      <c r="J22" s="16" t="n">
+      <c r="J22" s="25" t="n">
         <v>0.046</v>
       </c>
     </row>
-    <row r="23" s="17">
+    <row r="23" ht="19" customHeight="1" s="22">
       <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Site</t>
@@ -1381,7 +1522,7 @@
         <v>0.0065</v>
       </c>
     </row>
-    <row r="24" s="17">
+    <row r="24" ht="19" customHeight="1" s="22">
       <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Site/Genotype</t>
@@ -1416,10 +1557,10 @@
         </is>
       </c>
     </row>
-    <row r="25" s="17">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>Linear Mixed-Effects (Net Photosynthesis)</t>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Net Photosynthesis (Linear Mixed-Effects)</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
@@ -1450,13 +1591,13 @@
       <c r="I25" s="8" t="n">
         <v>0.0606</v>
       </c>
-      <c r="J25" s="16" t="inlineStr">
+      <c r="J25" s="25" t="inlineStr">
         <is>
           <t>0.086*</t>
         </is>
       </c>
     </row>
-    <row r="26" s="17">
+    <row r="26">
       <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Site</t>
@@ -1491,7 +1632,7 @@
         </is>
       </c>
     </row>
-    <row r="27" s="17">
+    <row r="27">
       <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Site/Genotype</t>
@@ -1526,10 +1667,10 @@
         </is>
       </c>
     </row>
-    <row r="28" s="17">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>Linear Mixed-Effects (Respiration)</t>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Respiration (Linear Mixed-Effects)</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
@@ -1560,13 +1701,13 @@
       <c r="I28" s="8" t="n">
         <v>0.0204</v>
       </c>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" s="17">
+      <c r="J28" s="25" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
       <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Site</t>
@@ -1601,7 +1742,7 @@
         </is>
       </c>
     </row>
-    <row r="30" s="17">
+    <row r="30">
       <c r="B30" s="11" t="inlineStr">
         <is>
           <t>Site/Genotype</t>
@@ -1636,10 +1777,10 @@
         </is>
       </c>
     </row>
-    <row r="31" s="17">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>Linear Mixed-Effects (Gross Photosynthesis)</t>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Gross Photosynthesis (Linear Mixed-Effects)</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
@@ -1670,11 +1811,11 @@
       <c r="I31" s="8" t="n">
         <v>0.08359999999999999</v>
       </c>
-      <c r="J31" s="16" t="n">
+      <c r="J31" s="25" t="n">
         <v>0.033</v>
       </c>
     </row>
-    <row r="32" s="17">
+    <row r="32">
       <c r="B32" s="11" t="inlineStr">
         <is>
           <t>Site</t>
@@ -1709,7 +1850,7 @@
         </is>
       </c>
     </row>
-    <row r="33" s="17">
+    <row r="33">
       <c r="B33" s="11" t="inlineStr">
         <is>
           <t>Site/Genotype</t>
@@ -1744,10 +1885,10 @@
         </is>
       </c>
     </row>
-    <row r="34" s="17">
-      <c r="A34" s="18" t="inlineStr">
-        <is>
-          <t>Linear Mixed-Effects (Photosynthesis:Respiration)</t>
+    <row r="34" ht="18" customHeight="1" s="22">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Photosynthesis: Respiration (Linear Mixed-Effects)</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
@@ -1778,11 +1919,11 @@
       <c r="I34" s="8" t="n">
         <v>0.1469</v>
       </c>
-      <c r="J34" s="16" t="n">
+      <c r="J34" s="25" t="n">
         <v>0.019</v>
       </c>
     </row>
-    <row r="35" s="17">
+    <row r="35" ht="18" customHeight="1" s="22">
       <c r="B35" s="11" t="inlineStr">
         <is>
           <t>Site</t>
@@ -1817,7 +1958,7 @@
         </is>
       </c>
     </row>
-    <row r="36" s="17">
+    <row r="36" ht="18" customHeight="1" s="22">
       <c r="B36" s="11" t="inlineStr">
         <is>
           <t>Site/Genotype</t>
@@ -1853,14 +1994,14 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
-        <is>
-          <t>PERMANOVA (Transcriptomics)</t>
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Transcriptomics (PERMANOVA)</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Colony (genotype)</t>
+          <t>Genotype</t>
         </is>
       </c>
       <c r="C37" s="14" t="n">
@@ -1890,16 +2031,16 @@
       <c r="I37" s="14" t="n">
         <v>0.467</v>
       </c>
-      <c r="J37" s="11" t="inlineStr">
+      <c r="J37" s="12" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
     </row>
-    <row r="38" s="17">
+    <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>Treatment (within colony)</t>
+          <t>Treatment</t>
         </is>
       </c>
       <c r="C38" s="14" t="n">
@@ -1925,16 +2066,16 @@
       <c r="I38" s="14" t="n">
         <v>0.07099999999999999</v>
       </c>
-      <c r="J38" s="11" t="inlineStr">
+      <c r="J38" s="12" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
       </c>
     </row>
-    <row r="39" s="17">
+    <row r="39">
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Site (colony means)</t>
+          <t>Site</t>
         </is>
       </c>
       <c r="C39" s="14" t="n">
@@ -1960,7 +2101,7 @@
       <c r="I39" s="14" t="n">
         <v>0.156</v>
       </c>
-      <c r="J39" s="11" t="inlineStr">
+      <c r="J39" s="12" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
@@ -1969,7 +2110,7 @@
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Urban vs Reef (colony means)</t>
+          <t>Urban vs Reef</t>
         </is>
       </c>
       <c r="C40" s="14" t="n">
@@ -1978,8 +2119,8 @@
       <c r="D40" s="15" t="n">
         <v>1.4387</v>
       </c>
-      <c r="E40" s="14" t="n">
-        <v>0.07000000000000001</v>
+      <c r="E40" s="27" t="n">
+        <v>0.0704</v>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
@@ -1995,7 +2136,7 @@
       <c r="I40" s="14" t="n">
         <v>0.059</v>
       </c>
-      <c r="J40" s="11" t="inlineStr">
+      <c r="J40" s="12" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
@@ -2010,13 +2151,13 @@
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A28:A30"/>
     <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A5:A7"/>
     <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="A37:A40"/>
     <mergeCell ref="A31:A33"/>
     <mergeCell ref="A11:A15"/>
-    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="A5:A7"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
